--- a/server/模板/样品导入模板.xlsx
+++ b/server/模板/样品导入模板.xlsx
@@ -397,20 +397,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:R1"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
-    <col min="2" max="2" width="7.83203125" customWidth="1"/>
-    <col min="3" max="3" width="7.83203125" customWidth="1"/>
-    <col min="4" max="4" width="7.83203125" customWidth="1"/>
+    <col min="2" max="2" width="10.83203125" customWidth="1"/>
+    <col min="3" max="3" width="10.83203125" customWidth="1"/>
+    <col min="4" max="4" width="10.83203125" customWidth="1"/>
     <col min="5" max="5" width="7.83203125" customWidth="1"/>
     <col min="6" max="6" width="7.83203125" customWidth="1"/>
     <col min="7" max="7" width="10.83203125" customWidth="1"/>
-    <col min="8" max="8" width="10.83203125" customWidth="1"/>
-    <col min="9" max="9" width="10.83203125" customWidth="1"/>
+    <col min="8" max="8" width="7.83203125" customWidth="1"/>
+    <col min="9" max="9" width="7.83203125" customWidth="1"/>
     <col min="10" max="10" width="7.83203125" customWidth="1"/>
-    <col min="11" max="11" width="10.83203125" customWidth="1"/>
+    <col min="11" max="11" width="7.83203125" customWidth="1"/>
     <col min="12" max="12" width="7.83203125" customWidth="1"/>
+    <col min="13" max="13" width="9.33203125" customWidth="1"/>
+    <col min="14" max="14" width="10.83203125" customWidth="1"/>
+    <col min="15" max="15" width="7.83203125" customWidth="1"/>
+    <col min="16" max="16" width="10.83203125" customWidth="1"/>
+    <col min="17" max="17" width="9.33203125" customWidth="1"/>
+    <col min="18" max="18" width="7.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -418,42 +424,60 @@
         <v>登记时间</v>
       </c>
       <c r="B1" t="str">
+        <v>物料编码</v>
+      </c>
+      <c r="C1" t="str">
+        <v>物料名称</v>
+      </c>
+      <c r="D1" t="str">
+        <v>物料规格</v>
+      </c>
+      <c r="E1" t="str">
         <v>品牌</v>
       </c>
-      <c r="C1" t="str">
+      <c r="F1" t="str">
         <v>尺寸</v>
       </c>
-      <c r="D1" t="str">
+      <c r="G1" t="str">
+        <v>PIN脚</v>
+      </c>
+      <c r="H1" t="str">
         <v>频点</v>
       </c>
-      <c r="E1" t="str">
+      <c r="I1" t="str">
         <v>负载</v>
       </c>
-      <c r="F1" t="str">
+      <c r="J1" t="str">
+        <v>电压</v>
+      </c>
+      <c r="K1" t="str">
         <v>模式</v>
       </c>
-      <c r="G1" t="str">
-        <v>物料编码</v>
-      </c>
-      <c r="H1" t="str">
-        <v>物料名称</v>
-      </c>
-      <c r="I1" t="str">
+      <c r="L1" t="str">
+        <v>频偏</v>
+      </c>
+      <c r="M1" t="str">
+        <v>含税价</v>
+      </c>
+      <c r="N1" t="str">
         <v>本价含税</v>
       </c>
-      <c r="J1" t="str">
+      <c r="O1" t="str">
         <v>工厂</v>
       </c>
-      <c r="K1" t="str">
+      <c r="P1" t="str">
         <v>库存数量</v>
       </c>
-      <c r="L1" t="str">
+      <c r="Q1" t="str">
+        <v>规格书</v>
+      </c>
+      <c r="R1" t="str">
         <v>备注</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:R1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/server/模板/样品导入模板.xlsx
+++ b/server/模板/样品导入模板.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R1"/>
+  <dimension ref="A1:S1"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
@@ -411,12 +411,13 @@
     <col min="10" max="10" width="7.83203125" customWidth="1"/>
     <col min="11" max="11" width="7.83203125" customWidth="1"/>
     <col min="12" max="12" width="7.83203125" customWidth="1"/>
-    <col min="13" max="13" width="9.33203125" customWidth="1"/>
-    <col min="14" max="14" width="10.83203125" customWidth="1"/>
-    <col min="15" max="15" width="7.83203125" customWidth="1"/>
-    <col min="16" max="16" width="10.83203125" customWidth="1"/>
-    <col min="17" max="17" width="9.33203125" customWidth="1"/>
-    <col min="18" max="18" width="7.83203125" customWidth="1"/>
+    <col min="13" max="13" width="7.83203125" customWidth="1"/>
+    <col min="14" max="14" width="9.33203125" customWidth="1"/>
+    <col min="15" max="15" width="10.83203125" customWidth="1"/>
+    <col min="16" max="16" width="7.83203125" customWidth="1"/>
+    <col min="17" max="17" width="10.83203125" customWidth="1"/>
+    <col min="18" max="18" width="9.33203125" customWidth="1"/>
+    <col min="19" max="19" width="7.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -457,27 +458,30 @@
         <v>频偏</v>
       </c>
       <c r="M1" t="str">
+        <v>温度</v>
+      </c>
+      <c r="N1" t="str">
         <v>含税价</v>
       </c>
-      <c r="N1" t="str">
+      <c r="O1" t="str">
         <v>本价含税</v>
       </c>
-      <c r="O1" t="str">
+      <c r="P1" t="str">
         <v>工厂</v>
       </c>
-      <c r="P1" t="str">
+      <c r="Q1" t="str">
         <v>库存数量</v>
       </c>
-      <c r="Q1" t="str">
+      <c r="R1" t="str">
         <v>规格书</v>
       </c>
-      <c r="R1" t="str">
+      <c r="S1" t="str">
         <v>备注</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:R1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S1"/>
   </ignoredErrors>
 </worksheet>
 </file>